--- a/data/PPA_scenario_definition.xlsx
+++ b/data/PPA_scenario_definition.xlsx
@@ -1529,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C70"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1544,9 +1544,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="7" customHeight="1">
-      <c r="B2" t="inlineStr"/>
-    </row>
+    <row r="2" ht="7" customHeight="1"/>
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="30" t="inlineStr">
         <is>
@@ -1575,9 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="7" customHeight="1">
-      <c r="B7" t="inlineStr"/>
-    </row>
+    <row r="7" ht="7" customHeight="1"/>
     <row r="8" ht="16" customHeight="1">
       <c r="B8" s="30" t="inlineStr">
         <is>
@@ -1627,9 +1623,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="7" customHeight="1">
-      <c r="B15" t="inlineStr"/>
-    </row>
+    <row r="15" ht="7" customHeight="1"/>
     <row r="16" ht="16" customHeight="1">
       <c r="B16" s="30" t="inlineStr">
         <is>
@@ -1644,9 +1638,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="7" customHeight="1">
-      <c r="B18" t="inlineStr"/>
-    </row>
+    <row r="18" ht="7" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
       <c r="B19" s="32" t="inlineStr">
         <is>
@@ -1668,9 +1660,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="7" customHeight="1">
-      <c r="B22" t="inlineStr"/>
-    </row>
+    <row r="22" ht="7" customHeight="1"/>
     <row r="23" ht="16" customHeight="1">
       <c r="B23" s="32" t="inlineStr">
         <is>
@@ -1692,9 +1682,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="7" customHeight="1">
-      <c r="B26" t="inlineStr"/>
-    </row>
+    <row r="26" ht="7" customHeight="1"/>
     <row r="27" ht="16" customHeight="1">
       <c r="B27" s="32" t="inlineStr">
         <is>
@@ -1716,9 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="7" customHeight="1">
-      <c r="B30" t="inlineStr"/>
-    </row>
+    <row r="30" ht="7" customHeight="1"/>
     <row r="31" ht="16" customHeight="1">
       <c r="B31" s="32" t="inlineStr">
         <is>
@@ -1740,9 +1726,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="7" customHeight="1">
-      <c r="B34" t="inlineStr"/>
-    </row>
+    <row r="34" ht="7" customHeight="1"/>
     <row r="35" ht="16" customHeight="1">
       <c r="B35" s="32" t="inlineStr">
         <is>
@@ -1764,9 +1748,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="7" customHeight="1">
-      <c r="B38" t="inlineStr"/>
-    </row>
+    <row r="38" ht="7" customHeight="1"/>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="32" t="inlineStr">
         <is>
@@ -1781,9 +1763,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="7" customHeight="1">
-      <c r="B41" t="inlineStr"/>
-    </row>
+    <row r="41" ht="7" customHeight="1"/>
     <row r="42" ht="16" customHeight="1">
       <c r="B42" s="30" t="inlineStr">
         <is>
@@ -1826,9 +1806,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="7" customHeight="1">
-      <c r="B48" t="inlineStr"/>
-    </row>
+    <row r="48" ht="7" customHeight="1"/>
     <row r="49" ht="16" customHeight="1">
       <c r="B49" s="30" t="inlineStr">
         <is>
@@ -1885,9 +1863,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="7" customHeight="1">
-      <c r="B57" t="inlineStr"/>
-    </row>
+    <row r="57" ht="7" customHeight="1"/>
     <row r="58" ht="16" customHeight="1">
       <c r="B58" s="30" t="inlineStr">
         <is>
@@ -1905,41 +1881,39 @@
     <row r="60" ht="16" customHeight="1">
       <c r="B60" s="31" t="inlineStr">
         <is>
-          <t>2. Right-click the file → Share → Copy link.</t>
+          <t>2. Note the path within your Drive (root = just the filename; subfolder = e.g. "pypsa-ppa/PPA_scenario_definition.xlsx").</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>3. Extract the file ID from the link:</t>
+          <t>3. In the notebook's scenario loading cell, set _GDRIVE_XLSX_PATH to that path.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   https://drive.google.com/file/d/&lt;FILE_ID&gt;/view</t>
+          <t xml:space="preserve">   _GDRIVE_XLSX_PATH = "PPA_scenario_definition.xlsx"</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="B63" s="31" t="inlineStr">
         <is>
-          <t>4. Paste the FILE_ID into the notebook cell that defines _SCENARIO_GDRIVE_FILE_ID.</t>
+          <t>4. Run the cell — it calls drive.mount() to connect your Drive, then reads the file directly.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="B64" s="31" t="inlineStr">
         <is>
-          <t>5. Run the notebook. The file will be downloaded automatically via gdown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="7" customHeight="1">
-      <c r="B65" t="inlineStr"/>
-    </row>
+          <t>5. Re-run the notebook from the scenario loading cell to pick up any edits to the Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="7" customHeight="1"/>
     <row r="66" ht="16" customHeight="1">
       <c r="B66" s="30" t="inlineStr">
         <is>

--- a/data/PPA_scenario_definition.xlsx
+++ b/data/PPA_scenario_definition.xlsx
@@ -1529,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="B1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1874,44 +1874,40 @@
     <row r="59" ht="16" customHeight="1">
       <c r="B59" s="31" t="inlineStr">
         <is>
-          <t>1. Upload this file to your Google Drive.</t>
+          <t>1. In Google Colab, open the file browser (folder icon in the left sidebar).</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="B60" s="31" t="inlineStr">
         <is>
-          <t>2. Note the path within your Drive (root = just the filename; subfolder = e.g. "pypsa-ppa/PPA_scenario_definition.xlsx").</t>
+          <t>2. Navigate into the data/ folder (or create it if it doesn't exist).</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>3. In the notebook's scenario loading cell, set _GDRIVE_XLSX_PATH to that path.</t>
+          <t>3. Right-click inside data/ and choose Upload, then select PPA_scenario_definition.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   _GDRIVE_XLSX_PATH = "PPA_scenario_definition.xlsx"</t>
+          <t>4. The notebook will find the file automatically at data/PPA_scenario_definition.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="B63" s="31" t="inlineStr">
         <is>
-          <t>4. Run the cell — it calls drive.mount() to connect your Drive, then reads the file directly.</t>
+          <t>5. Re-run the notebook from the scenario loading cell to pick up any edits.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>5. Re-run the notebook from the scenario loading cell to pick up any edits to the Excel.</t>
-        </is>
-      </c>
+      <c r="B64" s="31" t="inlineStr"/>
     </row>
     <row r="65" ht="7" customHeight="1"/>
     <row r="66" ht="16" customHeight="1">
